--- a/outputs/etf_trend_strategy/threshold_0.7/backtests/window_20/return_vol_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.7/backtests/window_20/return_vol_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
@@ -468,11 +468,11 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.04979332005439696</v>
+        <v>0.1811916041755057</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2831900754745529</v>
+        <v>0.1685666706299345</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.282696948430982</v>
+        <v>1.112285862073467</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.4008874102324168</v>
+        <v>1.667082006010314</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2085210001564898</v>
+        <v>0.08801699435797039</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2707079555795373</v>
+        <v>2.352385981542142</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>57.67126655829365</v>
+        <v>20.22107034610817</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.4292690773105271</v>
+        <v>0.1747074369505315</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2610263852260973</v>
+        <v>0.2786707728026878</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-2.161353321997343</v>
+        <v>0.6864991306178893</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-2.731419938745363</v>
+        <v>1.068527341734573</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4585960222969404</v>
+        <v>0.1242476899492491</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9645607758474032</v>
+        <v>1.469239618340297</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>53.40015295832262</v>
+        <v>48.81215356202862</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.1651276368580064</v>
+        <v>0.1483711905648066</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2238844233576173</v>
+        <v>0.230522510844363</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.7560588908253051</v>
+        <v>0.6755895466901508</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1.13314154983797</v>
+        <v>0.9612077949001724</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1610121500378895</v>
+        <v>0.1567543120232716</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1.071404047517549</v>
+        <v>0.9885208504578022</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>60.30183078820858</v>
+        <v>56.19048660945102</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.0844212314334376</v>
+        <v>0.2493220745066944</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2455489711596962</v>
+        <v>0.3468358286101929</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.4037837295000999</v>
+        <v>0.7974151202279562</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.6451943791944235</v>
+        <v>1.217178708954878</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2186770298374405</v>
+        <v>0.1770247889607821</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.4026900954511231</v>
+        <v>1.47361758933888</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>61.23067149806393</v>
+        <v>56.68032270332671</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.1587648403337873</v>
+        <v>0.1760828630522158</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2320234240072495</v>
+        <v>0.2603082022441113</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.710956524150723</v>
+        <v>0.7196717691407895</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.9777263847059687</v>
+        <v>1.008527838080558</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1552102449423166</v>
+        <v>0.2157181012795579</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.063758259073653</v>
+        <v>0.8491121826212462</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>68.40206231569995</v>
+        <v>66.69007400917518</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.3007919832253116</v>
+        <v>0.8700022410447616</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.2962875694427552</v>
+        <v>0.3687423051583229</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.707813370703985</v>
+        <v>3.225938349521542</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.571295912130383</v>
+        <v>5.541435977359897</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1478003681157704</v>
+        <v>0.09245953230123249</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.132889001933698</v>
+        <v>22.82665795897924</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>56.54914960561306</v>
+        <v>50.48688872107477</v>
       </c>
     </row>
   </sheetData>
